--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815599</v>
+        <v>119815626</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459201</v>
+        <v>458744</v>
       </c>
       <c r="R3" t="n">
-        <v>7072153</v>
+        <v>7072429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815626</v>
+        <v>119815599</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458744</v>
+        <v>459201</v>
       </c>
       <c r="R4" t="n">
-        <v>7072429</v>
+        <v>7072153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815626</v>
+        <v>119815599</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458744</v>
+        <v>459201</v>
       </c>
       <c r="R3" t="n">
-        <v>7072429</v>
+        <v>7072153</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815599</v>
+        <v>119815626</v>
       </c>
       <c r="B4" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459201</v>
+        <v>458744</v>
       </c>
       <c r="R4" t="n">
-        <v>7072153</v>
+        <v>7072429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815253</v>
+        <v>119815250</v>
       </c>
       <c r="B2" t="n">
         <v>74638</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459205</v>
+        <v>459128</v>
       </c>
       <c r="R2" t="n">
-        <v>7072139</v>
+        <v>7072192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815599</v>
+        <v>119815626</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459201</v>
+        <v>458744</v>
       </c>
       <c r="R3" t="n">
-        <v>7072153</v>
+        <v>7072429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815626</v>
+        <v>119815599</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458744</v>
+        <v>459201</v>
       </c>
       <c r="R4" t="n">
-        <v>7072429</v>
+        <v>7072153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815653</v>
+        <v>119815249</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459002</v>
+        <v>459188</v>
       </c>
       <c r="R5" t="n">
-        <v>7072284</v>
+        <v>7072160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815249</v>
+        <v>119815253</v>
       </c>
       <c r="B6" t="n">
         <v>74638</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459188</v>
+        <v>459205</v>
       </c>
       <c r="R6" t="n">
-        <v>7072160</v>
+        <v>7072139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815622</v>
+        <v>119815653</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459102</v>
+        <v>459002</v>
       </c>
       <c r="R8" t="n">
-        <v>7072194</v>
+        <v>7072284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815250</v>
+        <v>119815622</v>
       </c>
       <c r="B9" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459128</v>
+        <v>459102</v>
       </c>
       <c r="R9" t="n">
-        <v>7072192</v>
+        <v>7072194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815250</v>
+        <v>119815253</v>
       </c>
       <c r="B2" t="n">
         <v>74638</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459128</v>
+        <v>459205</v>
       </c>
       <c r="R2" t="n">
-        <v>7072192</v>
+        <v>7072139</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815626</v>
+        <v>119815653</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458744</v>
+        <v>459002</v>
       </c>
       <c r="R3" t="n">
-        <v>7072429</v>
+        <v>7072284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815249</v>
+        <v>119815250</v>
       </c>
       <c r="B5" t="n">
         <v>74638</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459188</v>
+        <v>459128</v>
       </c>
       <c r="R5" t="n">
-        <v>7072160</v>
+        <v>7072192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815253</v>
+        <v>119815356</v>
       </c>
       <c r="B6" t="n">
-        <v>74638</v>
+        <v>90509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459205</v>
+        <v>459127</v>
       </c>
       <c r="R6" t="n">
-        <v>7072139</v>
+        <v>7072178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815356</v>
+        <v>119815249</v>
       </c>
       <c r="B7" t="n">
-        <v>90509</v>
+        <v>74638</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459127</v>
+        <v>459188</v>
       </c>
       <c r="R7" t="n">
-        <v>7072178</v>
+        <v>7072160</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815653</v>
+        <v>119815622</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459002</v>
+        <v>459102</v>
       </c>
       <c r="R8" t="n">
-        <v>7072284</v>
+        <v>7072194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815622</v>
+        <v>119815626</v>
       </c>
       <c r="B9" t="n">
         <v>90580</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459102</v>
+        <v>458744</v>
       </c>
       <c r="R9" t="n">
-        <v>7072194</v>
+        <v>7072429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815253</v>
+        <v>119815653</v>
       </c>
       <c r="B2" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459205</v>
+        <v>459002</v>
       </c>
       <c r="R2" t="n">
-        <v>7072139</v>
+        <v>7072284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815653</v>
+        <v>119815253</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459002</v>
+        <v>459205</v>
       </c>
       <c r="R3" t="n">
-        <v>7072284</v>
+        <v>7072139</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815253</v>
+        <v>119815599</v>
       </c>
       <c r="B3" t="n">
-        <v>74638</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459205</v>
+        <v>459201</v>
       </c>
       <c r="R3" t="n">
-        <v>7072139</v>
+        <v>7072153</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815599</v>
+        <v>119815253</v>
       </c>
       <c r="B4" t="n">
-        <v>90576</v>
+        <v>74638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459201</v>
+        <v>459205</v>
       </c>
       <c r="R4" t="n">
-        <v>7072153</v>
+        <v>7072139</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815356</v>
+        <v>119815249</v>
       </c>
       <c r="B6" t="n">
-        <v>90509</v>
+        <v>74638</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459127</v>
+        <v>459188</v>
       </c>
       <c r="R6" t="n">
-        <v>7072178</v>
+        <v>7072160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815249</v>
+        <v>119815626</v>
       </c>
       <c r="B7" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459188</v>
+        <v>458744</v>
       </c>
       <c r="R7" t="n">
-        <v>7072160</v>
+        <v>7072429</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815622</v>
+        <v>119815356</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>90509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459102</v>
+        <v>459127</v>
       </c>
       <c r="R8" t="n">
-        <v>7072194</v>
+        <v>7072178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815626</v>
+        <v>119815622</v>
       </c>
       <c r="B9" t="n">
         <v>90580</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458744</v>
+        <v>459102</v>
       </c>
       <c r="R9" t="n">
-        <v>7072429</v>
+        <v>7072194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119815653</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815599</v>
+        <v>119815356</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459201</v>
+        <v>459127</v>
       </c>
       <c r="R3" t="n">
-        <v>7072153</v>
+        <v>7072178</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815253</v>
+        <v>119815599</v>
       </c>
       <c r="B4" t="n">
-        <v>74638</v>
+        <v>90594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459205</v>
+        <v>459201</v>
       </c>
       <c r="R4" t="n">
-        <v>7072139</v>
+        <v>7072153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815250</v>
+        <v>119815249</v>
       </c>
       <c r="B5" t="n">
-        <v>74638</v>
+        <v>74654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459128</v>
+        <v>459188</v>
       </c>
       <c r="R5" t="n">
-        <v>7072192</v>
+        <v>7072160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815249</v>
+        <v>119815253</v>
       </c>
       <c r="B6" t="n">
-        <v>74638</v>
+        <v>74654</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459188</v>
+        <v>459205</v>
       </c>
       <c r="R6" t="n">
-        <v>7072160</v>
+        <v>7072139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815626</v>
+        <v>119815250</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458744</v>
+        <v>459128</v>
       </c>
       <c r="R7" t="n">
-        <v>7072429</v>
+        <v>7072192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815356</v>
+        <v>119815622</v>
       </c>
       <c r="B8" t="n">
-        <v>90509</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459127</v>
+        <v>459102</v>
       </c>
       <c r="R8" t="n">
-        <v>7072178</v>
+        <v>7072194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815622</v>
+        <v>119815626</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459102</v>
+        <v>458744</v>
       </c>
       <c r="R9" t="n">
-        <v>7072194</v>
+        <v>7072429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815356</v>
+        <v>119815249</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>74654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459127</v>
+        <v>459188</v>
       </c>
       <c r="R3" t="n">
-        <v>7072178</v>
+        <v>7072160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815599</v>
+        <v>119815250</v>
       </c>
       <c r="B4" t="n">
-        <v>90594</v>
+        <v>74654</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459201</v>
+        <v>459128</v>
       </c>
       <c r="R4" t="n">
-        <v>7072153</v>
+        <v>7072192</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815249</v>
+        <v>119815626</v>
       </c>
       <c r="B5" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459188</v>
+        <v>458744</v>
       </c>
       <c r="R5" t="n">
-        <v>7072160</v>
+        <v>7072429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815250</v>
+        <v>119815622</v>
       </c>
       <c r="B7" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459128</v>
+        <v>459102</v>
       </c>
       <c r="R7" t="n">
-        <v>7072192</v>
+        <v>7072194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815622</v>
+        <v>119815356</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459102</v>
+        <v>459127</v>
       </c>
       <c r="R8" t="n">
-        <v>7072194</v>
+        <v>7072178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815626</v>
+        <v>119815599</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458744</v>
+        <v>459201</v>
       </c>
       <c r="R9" t="n">
-        <v>7072429</v>
+        <v>7072153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815653</v>
+        <v>119815249</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459002</v>
+        <v>459188</v>
       </c>
       <c r="R2" t="n">
-        <v>7072284</v>
+        <v>7072160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815249</v>
+        <v>119815626</v>
       </c>
       <c r="B3" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459188</v>
+        <v>458744</v>
       </c>
       <c r="R3" t="n">
-        <v>7072160</v>
+        <v>7072429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815626</v>
+        <v>119815622</v>
       </c>
       <c r="B5" t="n">
         <v>90598</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458744</v>
+        <v>459102</v>
       </c>
       <c r="R5" t="n">
-        <v>7072429</v>
+        <v>7072194</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815253</v>
+        <v>119815653</v>
       </c>
       <c r="B6" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459205</v>
+        <v>459002</v>
       </c>
       <c r="R6" t="n">
-        <v>7072139</v>
+        <v>7072284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815622</v>
+        <v>119815253</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459102</v>
+        <v>459205</v>
       </c>
       <c r="R7" t="n">
-        <v>7072194</v>
+        <v>7072139</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815356</v>
+        <v>119815599</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>90594</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459127</v>
+        <v>459201</v>
       </c>
       <c r="R8" t="n">
-        <v>7072178</v>
+        <v>7072153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815599</v>
+        <v>119815356</v>
       </c>
       <c r="B9" t="n">
-        <v>90594</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459201</v>
+        <v>459127</v>
       </c>
       <c r="R9" t="n">
-        <v>7072153</v>
+        <v>7072178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815249</v>
+        <v>119815356</v>
       </c>
       <c r="B2" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459188</v>
+        <v>459127</v>
       </c>
       <c r="R2" t="n">
-        <v>7072160</v>
+        <v>7072178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815626</v>
+        <v>119815538</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458744</v>
+        <v>458718</v>
       </c>
       <c r="R3" t="n">
-        <v>7072429</v>
+        <v>7072464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815250</v>
+        <v>119815653</v>
       </c>
       <c r="B4" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459128</v>
+        <v>459002</v>
       </c>
       <c r="R4" t="n">
-        <v>7072192</v>
+        <v>7072284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815622</v>
+        <v>119815656</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459102</v>
+        <v>459049</v>
       </c>
       <c r="R5" t="n">
-        <v>7072194</v>
+        <v>7072281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815653</v>
+        <v>119815249</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459002</v>
+        <v>459188</v>
       </c>
       <c r="R6" t="n">
-        <v>7072284</v>
+        <v>7072160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815253</v>
+        <v>119815250</v>
       </c>
       <c r="B7" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459205</v>
+        <v>459128</v>
       </c>
       <c r="R7" t="n">
-        <v>7072139</v>
+        <v>7072192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815599</v>
+        <v>119815713</v>
       </c>
       <c r="B8" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459201</v>
+        <v>458740</v>
       </c>
       <c r="R8" t="n">
-        <v>7072153</v>
+        <v>7072460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815356</v>
+        <v>119815599</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459127</v>
+        <v>459201</v>
       </c>
       <c r="R9" t="n">
-        <v>7072178</v>
+        <v>7072153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,6 +1476,107 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119815253</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fjällflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>459205</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7072139</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 72538-2021 artfynd.xlsx
+++ b/artfynd/A 72538-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815356</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815599</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815538</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815653</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815656</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815249</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815250</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815253</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,8 +1626,24 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815713</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>